--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>9.427463029870433</v>
+        <v>9.937089150742617</v>
       </c>
       <c r="D2" t="n">
-        <v>4.754803916582778</v>
+        <v>4.504878430294178</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>9.977797419182965</v>
+        <v>9.982776583987464</v>
       </c>
       <c r="G2" t="n">
-        <v>2.491685529360061</v>
+        <v>2.488592047955116</v>
       </c>
       <c r="H2" t="n">
         <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9112360850836945</v>
+        <v>0.7464405454688596</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,28 +540,28 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>9.784275952494259</v>
+        <v>9.962606227490326</v>
       </c>
       <c r="D3" t="n">
-        <v>5.810380600669648</v>
+        <v>5.803082792774061</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5387800932175</v>
+        <v>10.45786101650903</v>
       </c>
       <c r="G3" t="n">
-        <v>1.812271360163325</v>
+        <v>1.878011671914565</v>
       </c>
       <c r="H3" t="n">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4873039311684467</v>
+        <v>0.6558285567467566</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -568,28 +580,28 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>11.45075472610969</v>
+        <v>11.51112020113686</v>
       </c>
       <c r="D4" t="n">
-        <v>4.208448431183357</v>
+        <v>4.209219786585248</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>11.0483852375959</v>
+        <v>11.10074140530608</v>
       </c>
       <c r="G4" t="n">
-        <v>2.561594578022276</v>
+        <v>2.410994267651196</v>
       </c>
       <c r="H4" t="n">
         <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7903656408724601</v>
+        <v>0.7464405454688596</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>10.1300671276982</v>
+        <v>10.42164369673138</v>
       </c>
       <c r="D5" t="n">
-        <v>3.229015702817343</v>
+        <v>3.388800831783237</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>15.90655366516374</v>
+        <v>15.56603758052836</v>
       </c>
       <c r="G5" t="n">
-        <v>1.854806483731019</v>
+        <v>2.324148724516471</v>
       </c>
       <c r="H5" t="n">
         <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="J5" t="n">
-        <v>4.397771525257575e-07</v>
+        <v>8.664965198690906e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>1.319331457577273e-05</v>
+        <v>0.0002599489559607272</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,28 +660,28 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>13.45911300665833</v>
+        <v>14.01587175421211</v>
       </c>
       <c r="D6" t="n">
-        <v>4.664037269616939</v>
+        <v>4.313320264656184</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>12.62834777314463</v>
+        <v>12.60810696669622</v>
       </c>
       <c r="G6" t="n">
-        <v>2.893255116501725</v>
+        <v>2.889932994916852</v>
       </c>
       <c r="H6" t="n">
         <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2994482581488344</v>
+        <v>0.1097752830600092</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -688,28 +700,28 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>9.893290821434146</v>
+        <v>10.15204830173035</v>
       </c>
       <c r="D7" t="n">
-        <v>5.062007188356812</v>
+        <v>5.187522767230717</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>12.30119414494654</v>
+        <v>12.18558434367615</v>
       </c>
       <c r="G7" t="n">
-        <v>2.294876601491395</v>
+        <v>1.975599029136813</v>
       </c>
       <c r="H7" t="n">
         <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1247868780433192</v>
+        <v>0.3234041392359129</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -728,28 +740,28 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>11.26233872455717</v>
+        <v>11.73858064883243</v>
       </c>
       <c r="D8" t="n">
-        <v>4.163599920541812</v>
+        <v>4.215708283807253</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>9.64734964959675</v>
+        <v>9.763254939919472</v>
       </c>
       <c r="G8" t="n">
-        <v>1.786155681182531</v>
+        <v>1.934080808338971</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1837888581953325</v>
+        <v>0.07606639448563539</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -768,28 +780,28 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>11.15803091604725</v>
+        <v>11.90755689436094</v>
       </c>
       <c r="D9" t="n">
-        <v>4.903170594336381</v>
+        <v>4.669170219568286</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>13.7668221681493</v>
+        <v>13.74231826407564</v>
       </c>
       <c r="G9" t="n">
-        <v>3.893213630793177</v>
+        <v>3.902429949510284</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2200952071343677</v>
+        <v>0.4790418960574878</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -808,28 +820,28 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>10.48299745222157</v>
+        <v>10.63946662813576</v>
       </c>
       <c r="D10" t="n">
-        <v>3.066730167164884</v>
+        <v>2.973550018635885</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>11.25408937983144</v>
+        <v>11.28735145548896</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02491179414202</v>
+        <v>2.021851778549445</v>
       </c>
       <c r="H10" t="n">
         <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4055168116503611</v>
+        <v>0.5235167522208453</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -848,28 +860,28 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>9.921852263740167</v>
+        <v>10.42418134304041</v>
       </c>
       <c r="D11" t="n">
-        <v>3.922703720358729</v>
+        <v>3.88327730127067</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>11.65881101426638</v>
+        <v>11.72132495701407</v>
       </c>
       <c r="G11" t="n">
-        <v>2.180570866134254</v>
+        <v>2.149261440526509</v>
       </c>
       <c r="H11" t="n">
         <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06522684825505155</v>
+        <v>0.1444597552679135</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>11.05879262223332</v>
+        <v>11.3921570394347</v>
       </c>
       <c r="D12" t="n">
-        <v>3.600249132639135</v>
+        <v>3.398461033779226</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>15.7491528820766</v>
+        <v>15.62483564194299</v>
       </c>
       <c r="G12" t="n">
-        <v>1.210348144919714</v>
+        <v>1.416358480892943</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="J12" t="n">
-        <v>1.379652180246363e-06</v>
+        <v>5.290512959270561e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>4.13895654073909e-05</v>
+        <v>0.0001587153887781168</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>12.43284232501282</v>
+        <v>12.95181897700133</v>
       </c>
       <c r="D13" t="n">
-        <v>3.752229824352372</v>
+        <v>3.952962960190217</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>12.031331700178</v>
+        <v>12.01037017927823</v>
       </c>
       <c r="G13" t="n">
-        <v>1.979020250773006</v>
+        <v>1.974972532762031</v>
       </c>
       <c r="H13" t="n">
         <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7510251303301031</v>
+        <v>0.3966242821356912</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,28 +980,28 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>10.19110964027049</v>
+        <v>10.53694147408994</v>
       </c>
       <c r="D14" t="n">
-        <v>3.536987164871843</v>
+        <v>3.461854743350771</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>9.643789451879744</v>
+        <v>9.461550161126246</v>
       </c>
       <c r="G14" t="n">
-        <v>0.866328930782691</v>
+        <v>1.07938481640421</v>
       </c>
       <c r="H14" t="n">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2013456683306749</v>
+        <v>0.07321982439601583</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1008,28 +1020,28 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>12.60026435715917</v>
+        <v>12.70273243165479</v>
       </c>
       <c r="D15" t="n">
-        <v>2.661138611254342</v>
+        <v>2.666467694203978</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" t="n">
-        <v>13.33536400265943</v>
+        <v>13.52691487765181</v>
       </c>
       <c r="G15" t="n">
-        <v>2.406657355789449</v>
+        <v>2.078300928589377</v>
       </c>
       <c r="H15" t="n">
         <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4251563398706422</v>
+        <v>0.3234041392359129</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1048,28 +1060,28 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>9.065186068811018</v>
+        <v>9.503076080052717</v>
       </c>
       <c r="D16" t="n">
-        <v>3.093599169846863</v>
+        <v>3.103005888706239</v>
       </c>
       <c r="E16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>10.84455007329819</v>
+        <v>10.93136537650961</v>
       </c>
       <c r="G16" t="n">
-        <v>2.781989691922948</v>
+        <v>2.778120507263441</v>
       </c>
       <c r="H16" t="n">
         <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06776753662940209</v>
+        <v>0.1261917157968874</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1088,28 +1100,28 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>11.79816367936163</v>
+        <v>11.87850066732429</v>
       </c>
       <c r="D17" t="n">
-        <v>3.860641143078181</v>
+        <v>3.8878447836411</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" t="n">
-        <v>13.93170931935</v>
+        <v>13.96624048756911</v>
       </c>
       <c r="G17" t="n">
-        <v>1.666813138385813</v>
+        <v>1.705661787387582</v>
       </c>
       <c r="H17" t="n">
         <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07588181069627994</v>
+        <v>0.08515152604820063</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1128,28 +1140,28 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>11.34688654624644</v>
+        <v>11.89218557035982</v>
       </c>
       <c r="D18" t="n">
-        <v>5.480998767313737</v>
+        <v>5.560841412291207</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>11.75278427836149</v>
+        <v>11.8158132937692</v>
       </c>
       <c r="G18" t="n">
-        <v>2.201971168824873</v>
+        <v>2.226113038372612</v>
       </c>
       <c r="H18" t="n">
         <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2915314412674298</v>
+        <v>0.5235167522208453</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1168,28 +1180,28 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>11.34400686902084</v>
+        <v>11.62656130306168</v>
       </c>
       <c r="D19" t="n">
-        <v>4.532412258656007</v>
+        <v>4.175620986576754</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F19" t="n">
-        <v>9.766897626716636</v>
+        <v>9.802014738495615</v>
       </c>
       <c r="G19" t="n">
-        <v>2.820500202433201</v>
+        <v>2.767208994050204</v>
       </c>
       <c r="H19" t="n">
         <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09791588165087896</v>
+        <v>0.06269214394562003</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>10.85671548637146</v>
+        <v>11.22810026820464</v>
       </c>
       <c r="D20" t="n">
-        <v>3.828172461795963</v>
+        <v>3.961047341521143</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>13.38844359572972</v>
+        <v>13.25681503473246</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64338692900626</v>
+        <v>2.673539224713319</v>
       </c>
       <c r="H20" t="n">
         <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01673299999001452</v>
+        <v>0.06778802919779214</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5019899997004356</v>
+        <v>1</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1248,28 +1260,28 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>10.57051135414257</v>
+        <v>10.76146376817701</v>
       </c>
       <c r="D21" t="n">
-        <v>3.627713269256641</v>
+        <v>3.611551499122027</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
-        <v>10.63839940566639</v>
+        <v>10.87764213625063</v>
       </c>
       <c r="G21" t="n">
-        <v>1.941564848160339</v>
+        <v>1.970742142911546</v>
       </c>
       <c r="H21" t="n">
         <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0.979084688069229</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>9.692455858562919</v>
+        <v>10.19817571041182</v>
       </c>
       <c r="D22" t="n">
-        <v>4.245682717957066</v>
+        <v>4.278719462239627</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>13.60224483508997</v>
+        <v>13.40322889198127</v>
       </c>
       <c r="G22" t="n">
-        <v>1.845948120892396</v>
+        <v>2.043983100850315</v>
       </c>
       <c r="H22" t="n">
         <v>14</v>
       </c>
       <c r="I22" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002203047020035315</v>
+        <v>0.01099063250168482</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06609141060105944</v>
+        <v>0.3297189750505446</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>9.50241758000749</v>
+        <v>9.607959724699722</v>
       </c>
       <c r="D23" t="n">
-        <v>4.503938384154113</v>
+        <v>4.600756446673754</v>
       </c>
       <c r="E23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F23" t="n">
-        <v>12.32400605469563</v>
+        <v>12.25417149654004</v>
       </c>
       <c r="G23" t="n">
-        <v>1.562077543805184</v>
+        <v>1.583743382470067</v>
       </c>
       <c r="H23" t="n">
         <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01198527968200369</v>
+        <v>0.01704675424721766</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3595583904601106</v>
+        <v>0.5114026274165299</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1368,31 +1380,31 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>13.84020748116047</v>
+        <v>14.13647171546342</v>
       </c>
       <c r="D24" t="n">
-        <v>2.850790109764032</v>
+        <v>2.698506549433358</v>
       </c>
       <c r="E24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
-        <v>11.80985897636476</v>
+        <v>12.00136763863538</v>
       </c>
       <c r="G24" t="n">
-        <v>5.077280919070586</v>
+        <v>4.955059916734449</v>
       </c>
       <c r="H24" t="n">
         <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02634990795176147</v>
+        <v>0.02471191002297487</v>
       </c>
       <c r="K24" t="n">
-        <v>0.790497238552844</v>
+        <v>0.7413573006892461</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1408,34 +1420,34 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.401950379352064</v>
+        <v>9.93180523601743</v>
       </c>
       <c r="D25" t="n">
-        <v>4.020692123970704</v>
+        <v>3.871043352895756</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" t="n">
-        <v>13.17602608164337</v>
+        <v>13.0961297920741</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328187644424178</v>
+        <v>2.462496053089505</v>
       </c>
       <c r="H25" t="n">
         <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001153816729945738</v>
+        <v>0.002883072027772844</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03461450189837214</v>
+        <v>0.08649216083318532</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1448,19 +1460,19 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>10.36760548771193</v>
+        <v>10.68726442806161</v>
       </c>
       <c r="D26" t="n">
-        <v>3.328919049401041</v>
+        <v>3.064569479506983</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
-        <v>12.84148445259164</v>
+        <v>12.98345939041997</v>
       </c>
       <c r="G26" t="n">
-        <v>3.078693666322023</v>
+        <v>3.159497395142977</v>
       </c>
       <c r="H26" t="n">
         <v>14</v>
@@ -1469,10 +1481,10 @@
         <v>202</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03003993233391445</v>
+        <v>0.0367457367822608</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9011979700174336</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>8.294153674075385</v>
+        <v>8.25386847183665</v>
       </c>
       <c r="D27" t="n">
-        <v>4.225688560156299</v>
+        <v>4.292941826322908</v>
       </c>
       <c r="E27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" t="n">
-        <v>13.30070735809308</v>
+        <v>13.42968155216415</v>
       </c>
       <c r="G27" t="n">
-        <v>2.524945905957514</v>
+        <v>2.619316395886796</v>
       </c>
       <c r="H27" t="n">
         <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0001099646350540217</v>
+        <v>0.0001007515741882181</v>
       </c>
       <c r="K27" t="n">
-        <v>0.003298939051620652</v>
+        <v>0.003022547225646544</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,28 +1540,28 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>10.94146414602291</v>
+        <v>11.63896241401185</v>
       </c>
       <c r="D28" t="n">
-        <v>4.818223030233059</v>
+        <v>4.477731128988341</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
-        <v>9.815111525876699</v>
+        <v>9.779494445072084</v>
       </c>
       <c r="G28" t="n">
-        <v>1.448745869572891</v>
+        <v>1.407973842513529</v>
       </c>
       <c r="H28" t="n">
         <v>14</v>
       </c>
       <c r="I28" t="n">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2612800453756595</v>
+        <v>0.07606639448563539</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>9.911437644519559</v>
+        <v>10.1336017464311</v>
       </c>
       <c r="D29" t="n">
-        <v>3.696217486251415</v>
+        <v>3.77618158265638</v>
       </c>
       <c r="E29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n">
-        <v>16.06340955559478</v>
+        <v>16.07845780999381</v>
       </c>
       <c r="G29" t="n">
-        <v>2.458235089534104</v>
+        <v>2.469295230620499</v>
       </c>
       <c r="H29" t="n">
         <v>14</v>
       </c>
       <c r="I29" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J29" t="n">
-        <v>3.496519130940643e-06</v>
+        <v>6.243539972873352e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0001048955739282193</v>
+        <v>0.0001873061991862006</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,28 +1620,28 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>12.16644547631021</v>
+        <v>12.41972829271262</v>
       </c>
       <c r="D30" t="n">
-        <v>4.967382204201324</v>
+        <v>5.034173219195689</v>
       </c>
       <c r="E30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" t="n">
-        <v>13.39107743720405</v>
+        <v>13.37096249437558</v>
       </c>
       <c r="G30" t="n">
-        <v>2.872730531222124</v>
+        <v>2.900282627646016</v>
       </c>
       <c r="H30" t="n">
         <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5655967412496737</v>
+        <v>0.8270625477379128</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1648,28 +1660,28 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>11.1484687626484</v>
+        <v>11.26679622186557</v>
       </c>
       <c r="D31" t="n">
-        <v>3.053462881985777</v>
+        <v>3.163735137914485</v>
       </c>
       <c r="E31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F31" t="n">
-        <v>11.83951836840664</v>
+        <v>11.87383730972652</v>
       </c>
       <c r="G31" t="n">
-        <v>4.822167754802005</v>
+        <v>4.783664007991167</v>
       </c>
       <c r="H31" t="n">
         <v>14</v>
       </c>
       <c r="I31" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9521337742422126</v>
+        <v>0.7864653231039064</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>74.10990376539769</v>
+        <v>73.93592429579441</v>
       </c>
       <c r="D32" t="n">
-        <v>16.20891166310113</v>
+        <v>16.26177521928758</v>
       </c>
       <c r="E32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F32" t="n">
-        <v>85.60201586800362</v>
+        <v>84.96548791292268</v>
       </c>
       <c r="G32" t="n">
-        <v>6.661200986455211</v>
+        <v>6.74549462671672</v>
       </c>
       <c r="H32" t="n">
         <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01922853844385271</v>
+        <v>0.0367457367822608</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5768561533155815</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>70.96737256042398</v>
+        <v>71.43680212150991</v>
       </c>
       <c r="D33" t="n">
-        <v>9.850186103512128</v>
+        <v>10.33529393649201</v>
       </c>
       <c r="E33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
-        <v>76.11714298446766</v>
+        <v>76.23777842326375</v>
       </c>
       <c r="G33" t="n">
-        <v>5.216951975778596</v>
+        <v>5.286218710882591</v>
       </c>
       <c r="H33" t="n">
         <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03273961036432528</v>
+        <v>0.06519903507327188</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9821883109297584</v>
+        <v>1</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>69.27553698470309</v>
+        <v>69.27636414791021</v>
       </c>
       <c r="D34" t="n">
-        <v>9.222731645852106</v>
+        <v>9.416722342962361</v>
       </c>
       <c r="E34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F34" t="n">
-        <v>84.0469235964807</v>
+        <v>84.05294336296751</v>
       </c>
       <c r="G34" t="n">
-        <v>3.643450757412811</v>
+        <v>3.65941935487017</v>
       </c>
       <c r="H34" t="n">
         <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J34" t="n">
-        <v>2.722503184441539e-06</v>
+        <v>4.477692145731904e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>8.167509553324617e-05</v>
+        <v>0.0001343307643719571</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,31 +1820,31 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>71.17444422839976</v>
+        <v>71.10143795896872</v>
       </c>
       <c r="D35" t="n">
-        <v>11.84895093542067</v>
+        <v>11.65910772777309</v>
       </c>
       <c r="E35" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" t="n">
-        <v>78.11425163646565</v>
+        <v>79.29896716361522</v>
       </c>
       <c r="G35" t="n">
-        <v>6.510450023973584</v>
+        <v>5.891032673416521</v>
       </c>
       <c r="H35" t="n">
         <v>14</v>
       </c>
       <c r="I35" t="n">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03136485987591803</v>
+        <v>0.008100249944708503</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9409457962775408</v>
+        <v>0.2430074983412551</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1848,34 +1860,34 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>67.04180251895524</v>
+        <v>66.00519708833183</v>
       </c>
       <c r="D36" t="n">
-        <v>11.89852415844484</v>
+        <v>11.49461922597008</v>
       </c>
       <c r="E36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F36" t="n">
-        <v>77.80368605882923</v>
+        <v>77.96572288312932</v>
       </c>
       <c r="G36" t="n">
-        <v>6.819871906042926</v>
+        <v>6.973793086383428</v>
       </c>
       <c r="H36" t="n">
         <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="J36" t="n">
-        <v>0.004069261242278246</v>
+        <v>0.0008700509981609251</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1220778372683474</v>
+        <v>0.02610152994482776</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>74.05565709727668</v>
+        <v>72.98871239234151</v>
       </c>
       <c r="D37" t="n">
-        <v>11.2248925952352</v>
+        <v>11.72994121261554</v>
       </c>
       <c r="E37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F37" t="n">
-        <v>86.15444717406365</v>
+        <v>86.43393837939331</v>
       </c>
       <c r="G37" t="n">
-        <v>6.776450925113714</v>
+        <v>6.384004631740671</v>
       </c>
       <c r="H37" t="n">
         <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0004526478743079971</v>
+        <v>0.0002185744374558892</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01357943622923991</v>
+        <v>0.006557233123676677</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -1928,31 +1940,31 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>75.19315578761184</v>
+        <v>75.92917875959991</v>
       </c>
       <c r="D38" t="n">
-        <v>11.1958386410643</v>
+        <v>11.00611748835174</v>
       </c>
       <c r="E38" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n">
-        <v>82.9317475257071</v>
+        <v>83.32748637040568</v>
       </c>
       <c r="G38" t="n">
-        <v>5.823143050067576</v>
+        <v>5.717166272844623</v>
       </c>
       <c r="H38" t="n">
         <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="J38" t="n">
-        <v>0.02106769851992051</v>
+        <v>0.01963424935795081</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6320309555976151</v>
+        <v>0.5890274807385243</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1968,28 +1980,28 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>65.44520416646812</v>
+        <v>65.6953649714692</v>
       </c>
       <c r="D39" t="n">
-        <v>11.66363561229245</v>
+        <v>11.44684762487729</v>
       </c>
       <c r="E39" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F39" t="n">
-        <v>68.98938782047476</v>
+        <v>69.3565498143587</v>
       </c>
       <c r="G39" t="n">
-        <v>10.14193629065019</v>
+        <v>10.80245440413426</v>
       </c>
       <c r="H39" t="n">
         <v>14</v>
       </c>
       <c r="I39" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2686312641480821</v>
+        <v>0.298377284652972</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -2008,31 +2020,31 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>74.073419894184</v>
+        <v>74.51681145521455</v>
       </c>
       <c r="D40" t="n">
-        <v>10.22840175190839</v>
+        <v>10.35942930307339</v>
       </c>
       <c r="E40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n">
-        <v>83.16552971154967</v>
+        <v>82.50681025754773</v>
       </c>
       <c r="G40" t="n">
-        <v>7.22723842339676</v>
+        <v>7.05547016574861</v>
       </c>
       <c r="H40" t="n">
         <v>14</v>
       </c>
       <c r="I40" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00345349192182495</v>
+        <v>0.01155275748398303</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1036047576547485</v>
+        <v>0.346582724519491</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2048,31 +2060,31 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>70.65721126250264</v>
+        <v>70.84729875119884</v>
       </c>
       <c r="D41" t="n">
-        <v>10.53432591250457</v>
+        <v>10.70354243233423</v>
       </c>
       <c r="E41" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" t="n">
-        <v>79.61316264805046</v>
+        <v>79.55293361409539</v>
       </c>
       <c r="G41" t="n">
-        <v>6.307690393573362</v>
+        <v>6.182157797160526</v>
       </c>
       <c r="H41" t="n">
         <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J41" t="n">
-        <v>0.007654676306132831</v>
+        <v>0.008100249944708503</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2296402891839849</v>
+        <v>0.2430074983412551</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>69.1815359358534</v>
+        <v>68.91970461858401</v>
       </c>
       <c r="D42" t="n">
-        <v>10.92986373942472</v>
+        <v>10.81401115554017</v>
       </c>
       <c r="E42" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F42" t="n">
-        <v>74.85354272398042</v>
+        <v>75.71335274082023</v>
       </c>
       <c r="G42" t="n">
-        <v>9.923958043219196</v>
+        <v>10.86398967062867</v>
       </c>
       <c r="H42" t="n">
         <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1290555242904612</v>
+        <v>0.07900260260114905</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>61.25567951667426</v>
+        <v>61.67093349513321</v>
       </c>
       <c r="D43" t="n">
-        <v>10.55756066976774</v>
+        <v>10.82091106451118</v>
       </c>
       <c r="E43" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F43" t="n">
-        <v>79.31418155799255</v>
+        <v>78.89493564909016</v>
       </c>
       <c r="G43" t="n">
-        <v>8.836876187007149</v>
+        <v>8.293496425375471</v>
       </c>
       <c r="H43" t="n">
         <v>14</v>
       </c>
       <c r="I43" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J43" t="n">
-        <v>1.004023642249987e-05</v>
+        <v>1.92615902407782e-05</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0003012070926749961</v>
+        <v>0.000577847707223346</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,31 +2180,31 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>73.23405737204413</v>
+        <v>72.37135125238672</v>
       </c>
       <c r="D44" t="n">
-        <v>10.59078801441257</v>
+        <v>9.935369855044842</v>
       </c>
       <c r="E44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
-        <v>83.72671492919415</v>
+        <v>84.05777846233632</v>
       </c>
       <c r="G44" t="n">
-        <v>5.518343143833549</v>
+        <v>4.998505058780316</v>
       </c>
       <c r="H44" t="n">
         <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0009045038840725239</v>
+        <v>0.0001007515741882181</v>
       </c>
       <c r="K44" t="n">
-        <v>0.02713511652217572</v>
+        <v>0.003022547225646544</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>68.26408136162631</v>
+        <v>68.70897578174753</v>
       </c>
       <c r="D45" t="n">
-        <v>10.06861832835716</v>
+        <v>10.25828945873887</v>
       </c>
       <c r="E45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F45" t="n">
-        <v>80.81769530534011</v>
+        <v>80.11727665314577</v>
       </c>
       <c r="G45" t="n">
-        <v>5.078669081722857</v>
+        <v>5.260225974136457</v>
       </c>
       <c r="H45" t="n">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="J45" t="n">
-        <v>8.282148344235213e-05</v>
+        <v>0.0002871663489101762</v>
       </c>
       <c r="K45" t="n">
-        <v>0.002484644503270564</v>
+        <v>0.008614990467305286</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>75.54926825756115</v>
+        <v>75.78098151167485</v>
       </c>
       <c r="D46" t="n">
-        <v>12.75152279426374</v>
+        <v>12.29959184156758</v>
       </c>
       <c r="E46" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F46" t="n">
-        <v>83.78164529838641</v>
+        <v>83.7371345005611</v>
       </c>
       <c r="G46" t="n">
-        <v>8.229357004575341</v>
+        <v>8.234470844987376</v>
       </c>
       <c r="H46" t="n">
         <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02411344132180038</v>
+        <v>0.02255839436981481</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7234032396540114</v>
+        <v>0.6767518310944444</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>66.95144273964949</v>
+        <v>66.80172631201022</v>
       </c>
       <c r="D47" t="n">
-        <v>10.53835370779806</v>
+        <v>10.93546758727303</v>
       </c>
       <c r="E47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F47" t="n">
-        <v>78.22113114978491</v>
+        <v>78.59182429593511</v>
       </c>
       <c r="G47" t="n">
-        <v>5.124644198491293</v>
+        <v>4.715288742853669</v>
       </c>
       <c r="H47" t="n">
         <v>14</v>
       </c>
       <c r="I47" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0003725954989106279</v>
+        <v>0.0003755431778003455</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01117786496731884</v>
+        <v>0.01126629533401037</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>66.88704239169356</v>
+        <v>66.57354546978418</v>
       </c>
       <c r="D48" t="n">
-        <v>10.33490313168947</v>
+        <v>10.77318467722787</v>
       </c>
       <c r="E48" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F48" t="n">
-        <v>74.95754712494775</v>
+        <v>74.72841066213502</v>
       </c>
       <c r="G48" t="n">
-        <v>3.282810687189079</v>
+        <v>3.399979985991083</v>
       </c>
       <c r="H48" t="n">
         <v>14</v>
       </c>
       <c r="I48" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J48" t="n">
-        <v>0.002080102602813595</v>
+        <v>0.002426412521148466</v>
       </c>
       <c r="K48" t="n">
-        <v>0.06240307808440785</v>
+        <v>0.07279237563445398</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>74.34857932278709</v>
+        <v>74.28393779423357</v>
       </c>
       <c r="D49" t="n">
-        <v>9.632889722166226</v>
+        <v>10.04711798192897</v>
       </c>
       <c r="E49" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F49" t="n">
-        <v>82.54603478333591</v>
+        <v>81.98778354349022</v>
       </c>
       <c r="G49" t="n">
-        <v>6.126375706421045</v>
+        <v>7.301593115519884</v>
       </c>
       <c r="H49" t="n">
         <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J49" t="n">
-        <v>0.005045109824883479</v>
+        <v>0.01339519196558679</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1513532947465044</v>
+        <v>0.4018557589676037</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.59914747867013</v>
+        <v>75.61213680415288</v>
       </c>
       <c r="D50" t="n">
-        <v>7.911906275961754</v>
+        <v>7.902533756597535</v>
       </c>
       <c r="E50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>85.36533262253977</v>
+        <v>85.41515989967102</v>
       </c>
       <c r="G50" t="n">
-        <v>4.606930514218465</v>
+        <v>4.632964992731474</v>
       </c>
       <c r="H50" t="n">
         <v>14</v>
       </c>
       <c r="I50" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J50" t="n">
-        <v>3.998047285665204e-05</v>
+        <v>3.573398811649717e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.001199414185699561</v>
+        <v>0.001072019643494915</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>67.02547188936579</v>
+        <v>67.12544653219803</v>
       </c>
       <c r="D51" t="n">
-        <v>7.715711121678723</v>
+        <v>7.684241574263293</v>
       </c>
       <c r="E51" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F51" t="n">
-        <v>79.84646771395535</v>
+        <v>80.00733497477177</v>
       </c>
       <c r="G51" t="n">
-        <v>4.6663273029828</v>
+        <v>4.367760639681171</v>
       </c>
       <c r="H51" t="n">
         <v>14</v>
       </c>
       <c r="I51" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J51" t="n">
-        <v>3.217632700621217e-06</v>
+        <v>2.69561896984408e-06</v>
       </c>
       <c r="K51" t="n">
-        <v>9.652898101863651e-05</v>
+        <v>8.086856909532241e-05</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,31 +2500,31 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>70.44768316513773</v>
+        <v>70.05454205169194</v>
       </c>
       <c r="D52" t="n">
-        <v>9.605778983565843</v>
+        <v>9.441182421841324</v>
       </c>
       <c r="E52" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F52" t="n">
-        <v>78.45129504700894</v>
+        <v>79.22656034034091</v>
       </c>
       <c r="G52" t="n">
-        <v>5.756708497070031</v>
+        <v>6.698933155257848</v>
       </c>
       <c r="H52" t="n">
         <v>14</v>
       </c>
       <c r="I52" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="J52" t="n">
-        <v>0.005910833670588748</v>
+        <v>0.001809992988212863</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1773250101176624</v>
+        <v>0.05429978964638588</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>73.44579953202137</v>
+        <v>73.34179081122615</v>
       </c>
       <c r="D53" t="n">
-        <v>9.561640962098521</v>
+        <v>9.376575883836846</v>
       </c>
       <c r="E53" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F53" t="n">
-        <v>84.11549564571021</v>
+        <v>84.28093040047577</v>
       </c>
       <c r="G53" t="n">
-        <v>5.885876829226016</v>
+        <v>5.949931982591703</v>
       </c>
       <c r="H53" t="n">
         <v>14</v>
       </c>
       <c r="I53" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0003489973135455016</v>
+        <v>0.0002040101254528767</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01046991940636505</v>
+        <v>0.006120303763586301</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,28 +2580,28 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>67.68305240738492</v>
+        <v>67.64455078498059</v>
       </c>
       <c r="D54" t="n">
-        <v>10.07328396174769</v>
+        <v>9.507172149280583</v>
       </c>
       <c r="E54" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F54" t="n">
-        <v>68.29491612750404</v>
+        <v>67.5476680759689</v>
       </c>
       <c r="G54" t="n">
-        <v>9.488366152315052</v>
+        <v>8.967241087576218</v>
       </c>
       <c r="H54" t="n">
         <v>14</v>
       </c>
       <c r="I54" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9112360850836945</v>
+        <v>0.9095511968114011</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>68.5834535199312</v>
+        <v>69.16035257649466</v>
       </c>
       <c r="D55" t="n">
-        <v>12.15456400439423</v>
+        <v>12.09870273263603</v>
       </c>
       <c r="E55" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F55" t="n">
-        <v>75.81857162890171</v>
+        <v>75.68187947765641</v>
       </c>
       <c r="G55" t="n">
-        <v>8.707570881766122</v>
+        <v>8.539261237152347</v>
       </c>
       <c r="H55" t="n">
         <v>14</v>
       </c>
       <c r="I55" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J55" t="n">
-        <v>0.03136485987591803</v>
+        <v>0.05564552356859782</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9409457962775408</v>
+        <v>1</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>61.76599009059306</v>
+        <v>62.59030613384117</v>
       </c>
       <c r="D56" t="n">
-        <v>9.946247549980427</v>
+        <v>11.29925754042251</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F56" t="n">
-        <v>76.27635968913593</v>
+        <v>75.99746294736504</v>
       </c>
       <c r="G56" t="n">
-        <v>10.05143642339737</v>
+        <v>9.950722339451668</v>
       </c>
       <c r="H56" t="n">
         <v>14</v>
       </c>
       <c r="I56" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="J56" t="n">
-        <v>8.282148344235213e-05</v>
+        <v>0.0004578665987864235</v>
       </c>
       <c r="K56" t="n">
-        <v>0.002484644503270564</v>
+        <v>0.0137359979635927</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,28 +2700,28 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>72.10637113311651</v>
+        <v>72.29028459111255</v>
       </c>
       <c r="D57" t="n">
-        <v>11.75275409547123</v>
+        <v>11.71095442087469</v>
       </c>
       <c r="E57" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F57" t="n">
-        <v>78.64725734506177</v>
+        <v>78.26398635691727</v>
       </c>
       <c r="G57" t="n">
-        <v>6.685247774797425</v>
+        <v>7.289425907871781</v>
       </c>
       <c r="H57" t="n">
         <v>14</v>
       </c>
       <c r="I57" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="J57" t="n">
-        <v>0.04571053903140908</v>
+        <v>0.07606639448563539</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>67.44865477934029</v>
+        <v>67.27501443915367</v>
       </c>
       <c r="D58" t="n">
-        <v>9.600760656865161</v>
+        <v>9.656121135404439</v>
       </c>
       <c r="E58" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F58" t="n">
-        <v>82.26338962932711</v>
+        <v>82.36082317478864</v>
       </c>
       <c r="G58" t="n">
-        <v>4.691776655351063</v>
+        <v>4.71484654301811</v>
       </c>
       <c r="H58" t="n">
         <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J58" t="n">
-        <v>1.004023642249987e-05</v>
+        <v>1.018990537840821e-05</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0003012070926749961</v>
+        <v>0.0003056971613522464</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>72.6004808549918</v>
+        <v>72.50598323085751</v>
       </c>
       <c r="D59" t="n">
-        <v>10.30812152653498</v>
+        <v>10.49401935727769</v>
       </c>
       <c r="E59" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F59" t="n">
-        <v>71.74673171322146</v>
+        <v>72.14319282146212</v>
       </c>
       <c r="G59" t="n">
-        <v>6.101938536192917</v>
+        <v>5.71842416672139</v>
       </c>
       <c r="H59" t="n">
         <v>14</v>
       </c>
       <c r="I59" t="n">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9521337742422126</v>
+        <v>0.7730550731613904</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>68.40554165526652</v>
+        <v>68.81747412853133</v>
       </c>
       <c r="D60" t="n">
-        <v>10.6087744292561</v>
+        <v>10.72652388287278</v>
       </c>
       <c r="E60" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F60" t="n">
-        <v>76.39965181849426</v>
+        <v>76.3737974945969</v>
       </c>
       <c r="G60" t="n">
-        <v>7.203988274287767</v>
+        <v>7.144041864080103</v>
       </c>
       <c r="H60" t="n">
         <v>14</v>
       </c>
       <c r="I60" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0201297955752651</v>
+        <v>0.02827542454858545</v>
       </c>
       <c r="K60" t="n">
-        <v>0.603893867257953</v>
+        <v>0.8482627364575634</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>69.04022941070438</v>
+        <v>68.83811577284121</v>
       </c>
       <c r="D61" t="n">
-        <v>10.0543029724643</v>
+        <v>10.33482005789997</v>
       </c>
       <c r="E61" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F61" t="n">
-        <v>78.51466808040759</v>
+        <v>77.89744140793293</v>
       </c>
       <c r="G61" t="n">
-        <v>8.15783064993334</v>
+        <v>7.875080966893388</v>
       </c>
       <c r="H61" t="n">
         <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J61" t="n">
-        <v>0.002080102602813595</v>
+        <v>0.003051916004182555</v>
       </c>
       <c r="K61" t="n">
-        <v>0.06240307808440785</v>
+        <v>0.09155748012547665</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>97.62749372180805</v>
+        <v>98.19169765810523</v>
       </c>
       <c r="D62" t="n">
-        <v>22.34518202695796</v>
+        <v>22.91149335530206</v>
       </c>
       <c r="E62" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F62" t="n">
-        <v>101.9741575350771</v>
+        <v>101.6580409203021</v>
       </c>
       <c r="G62" t="n">
-        <v>7.752173049837036</v>
+        <v>7.681027296399193</v>
       </c>
       <c r="H62" t="n">
         <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8302478199687978</v>
+        <v>0.6558285567467566</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>102.7839269862871</v>
+        <v>102.9244478765427</v>
       </c>
       <c r="D63" t="n">
-        <v>13.09796866078064</v>
+        <v>13.57968373812297</v>
       </c>
       <c r="E63" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F63" t="n">
-        <v>33.64724596660058</v>
+        <v>33.67685657676596</v>
       </c>
       <c r="G63" t="n">
-        <v>6.734095188365615</v>
+        <v>6.814195252768402</v>
       </c>
       <c r="H63" t="n">
         <v>14</v>
       </c>
       <c r="I63" t="n">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="J63" t="n">
-        <v>1.760722132370437e-08</v>
+        <v>1.919980325303849e-08</v>
       </c>
       <c r="K63" t="n">
-        <v>5.28216639711131e-07</v>
+        <v>5.759940975911548e-07</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,34 +2980,34 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>81.2824846583277</v>
+        <v>79.05313983681792</v>
       </c>
       <c r="D64" t="n">
-        <v>23.83313043542575</v>
+        <v>23.01089556317993</v>
       </c>
       <c r="E64" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>102.6913792406289</v>
+        <v>102.4329687436818</v>
       </c>
       <c r="G64" t="n">
-        <v>10.98271050452084</v>
+        <v>10.52786581832921</v>
       </c>
       <c r="H64" t="n">
         <v>14</v>
       </c>
       <c r="I64" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="J64" t="n">
-        <v>0.001748047475450262</v>
+        <v>0.0004287174191554415</v>
       </c>
       <c r="K64" t="n">
-        <v>0.05244142426350785</v>
+        <v>0.01286152257466325</v>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>102.2050295391172</v>
+        <v>102.4410977245595</v>
       </c>
       <c r="D65" t="n">
-        <v>15.07100606112629</v>
+        <v>15.21232779484898</v>
       </c>
       <c r="E65" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F65" t="n">
-        <v>51.55424406615175</v>
+        <v>52.2844397719461</v>
       </c>
       <c r="G65" t="n">
-        <v>10.55644243781731</v>
+        <v>11.68481326589217</v>
       </c>
       <c r="H65" t="n">
         <v>14</v>
       </c>
       <c r="I65" t="n">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="J65" t="n">
-        <v>2.147189782813519e-08</v>
+        <v>3.171911117025865e-08</v>
       </c>
       <c r="K65" t="n">
-        <v>6.441569348440557e-07</v>
+        <v>9.515733351077596e-07</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>76.83692937711889</v>
+        <v>75.41852545564166</v>
       </c>
       <c r="D66" t="n">
-        <v>24.75571776611702</v>
+        <v>23.74429431521089</v>
       </c>
       <c r="E66" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F66" t="n">
-        <v>76.44518782095341</v>
+        <v>76.03189761837366</v>
       </c>
       <c r="G66" t="n">
-        <v>10.53885259412426</v>
+        <v>9.800941170124165</v>
       </c>
       <c r="H66" t="n">
         <v>14</v>
       </c>
       <c r="I66" t="n">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8436451751000998</v>
+        <v>0.7332436358759638</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,28 +3100,28 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>104.4134981421367</v>
+        <v>102.1059331274071</v>
       </c>
       <c r="D67" t="n">
-        <v>16.262782557116</v>
+        <v>18.09047806931048</v>
       </c>
       <c r="E67" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F67" t="n">
-        <v>115.4293097731587</v>
+        <v>115.0527811249034</v>
       </c>
       <c r="G67" t="n">
-        <v>5.697624965396966</v>
+        <v>5.728597336042378</v>
       </c>
       <c r="H67" t="n">
         <v>14</v>
       </c>
       <c r="I67" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J67" t="n">
-        <v>0.04760184257209995</v>
+        <v>0.04173579952502548</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>98.63687180444545</v>
+        <v>100.3272810396385</v>
       </c>
       <c r="D68" t="n">
-        <v>16.25091909031554</v>
+        <v>15.36491481684395</v>
       </c>
       <c r="E68" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F68" t="n">
-        <v>93.01214225061644</v>
+        <v>93.11009866159861</v>
       </c>
       <c r="G68" t="n">
-        <v>13.28664676781644</v>
+        <v>13.26788304885073</v>
       </c>
       <c r="H68" t="n">
         <v>14</v>
       </c>
       <c r="I68" t="n">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="J68" t="n">
-        <v>0.1621785444598234</v>
+        <v>0.07046099865783068</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>80.10194831708324</v>
+        <v>79.49290798557692</v>
       </c>
       <c r="D69" t="n">
-        <v>14.80422705395564</v>
+        <v>14.90585452283374</v>
       </c>
       <c r="E69" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F69" t="n">
-        <v>42.11777970967607</v>
+        <v>42.29708503497631</v>
       </c>
       <c r="G69" t="n">
-        <v>5.382772908843439</v>
+        <v>5.608970125787116</v>
       </c>
       <c r="H69" t="n">
         <v>14</v>
       </c>
       <c r="I69" t="n">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="J69" t="n">
-        <v>4.261718428669779e-08</v>
+        <v>4.714311015399655e-08</v>
       </c>
       <c r="K69" t="n">
-        <v>1.278515528600934e-06</v>
+        <v>1.414293304619897e-06</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,31 +3220,31 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>100.5346393577874</v>
+        <v>101.6768855142197</v>
       </c>
       <c r="D70" t="n">
-        <v>17.23417674440824</v>
+        <v>17.86182866808021</v>
       </c>
       <c r="E70" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F70" t="n">
-        <v>74.95686789858873</v>
+        <v>74.51585783025344</v>
       </c>
       <c r="G70" t="n">
-        <v>28.66583877273825</v>
+        <v>28.41683136180926</v>
       </c>
       <c r="H70" t="n">
         <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J70" t="n">
-        <v>0.007272873630891749</v>
+        <v>0.004039358066150299</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2181862089267524</v>
+        <v>0.121180741984509</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3248,28 +3260,28 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>89.42282563790627</v>
+        <v>90.04829717323601</v>
       </c>
       <c r="D71" t="n">
-        <v>19.51324747209382</v>
+        <v>20.49415313786295</v>
       </c>
       <c r="E71" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F71" t="n">
-        <v>87.69037159839867</v>
+        <v>87.1912187133556</v>
       </c>
       <c r="G71" t="n">
-        <v>14.26217601868346</v>
+        <v>13.23620893796611</v>
       </c>
       <c r="H71" t="n">
         <v>14</v>
       </c>
       <c r="I71" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9248479363518587</v>
+        <v>0.8681273814047451</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>90.95061204087875</v>
+        <v>89.60905573536446</v>
       </c>
       <c r="D72" t="n">
-        <v>20.78587504820067</v>
+        <v>20.36804936916706</v>
       </c>
       <c r="E72" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F72" t="n">
-        <v>28.60248958796648</v>
+        <v>31.55980105939905</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0066442549175</v>
+        <v>21.35236496438176</v>
       </c>
       <c r="H72" t="n">
         <v>14</v>
       </c>
       <c r="I72" t="n">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="J72" t="n">
-        <v>3.508686954678543e-08</v>
+        <v>4.599719691755257e-07</v>
       </c>
       <c r="K72" t="n">
-        <v>1.052606086403563e-06</v>
+        <v>1.379915907526577e-05</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>64.01631715557258</v>
+        <v>64.77437920722615</v>
       </c>
       <c r="D73" t="n">
-        <v>31.01298573156362</v>
+        <v>31.92953053218244</v>
       </c>
       <c r="E73" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F73" t="n">
-        <v>103.4291569285509</v>
+        <v>103.0496627714202</v>
       </c>
       <c r="G73" t="n">
-        <v>19.34111504567739</v>
+        <v>19.11479134287599</v>
       </c>
       <c r="H73" t="n">
         <v>14</v>
       </c>
       <c r="I73" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0001912693027698364</v>
+        <v>0.0005217942805924886</v>
       </c>
       <c r="K73" t="n">
-        <v>0.005738079083095092</v>
+        <v>0.01565382841777466</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>98.22460605476601</v>
+        <v>95.43838257916019</v>
       </c>
       <c r="D74" t="n">
-        <v>23.73498361080526</v>
+        <v>23.41130961696738</v>
       </c>
       <c r="E74" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F74" t="n">
-        <v>82.4149658323561</v>
+        <v>82.06094537220488</v>
       </c>
       <c r="G74" t="n">
-        <v>14.98843170841357</v>
+        <v>14.67309024591507</v>
       </c>
       <c r="H74" t="n">
         <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>462</v>
+        <v>429</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02305827967616613</v>
+        <v>0.06269214394562003</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6917483902849838</v>
+        <v>1</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>77.61904728065468</v>
+        <v>78.06145485423146</v>
       </c>
       <c r="D75" t="n">
-        <v>12.38323843844565</v>
+        <v>12.51918342306621</v>
       </c>
       <c r="E75" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F75" t="n">
-        <v>37.46445432857543</v>
+        <v>37.11878613885403</v>
       </c>
       <c r="G75" t="n">
-        <v>14.66994851642971</v>
+        <v>14.06859496476934</v>
       </c>
       <c r="H75" t="n">
         <v>14</v>
       </c>
       <c r="I75" t="n">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="J75" t="n">
-        <v>8.340940901116819e-08</v>
+        <v>6.326119468285779e-08</v>
       </c>
       <c r="K75" t="n">
-        <v>2.502282270335046e-06</v>
+        <v>1.897835840485734e-06</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,28 +3460,28 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>103.4919925805924</v>
+        <v>103.5991309270355</v>
       </c>
       <c r="D76" t="n">
-        <v>17.79503596167152</v>
+        <v>17.88595278125909</v>
       </c>
       <c r="E76" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F76" t="n">
-        <v>112.6655036189396</v>
+        <v>112.3953422829645</v>
       </c>
       <c r="G76" t="n">
-        <v>20.38900094527706</v>
+        <v>20.39685634500964</v>
       </c>
       <c r="H76" t="n">
         <v>14</v>
       </c>
       <c r="I76" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1290555242904612</v>
+        <v>0.1594422268115424</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>78.8224019126653</v>
+        <v>78.61696045976437</v>
       </c>
       <c r="D77" t="n">
-        <v>14.77763835766491</v>
+        <v>15.27004172734859</v>
       </c>
       <c r="E77" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F77" t="n">
-        <v>90.35279406412987</v>
+        <v>90.17496502365437</v>
       </c>
       <c r="G77" t="n">
-        <v>16.28338350646273</v>
+        <v>16.55232723825028</v>
       </c>
       <c r="H77" t="n">
         <v>14</v>
       </c>
       <c r="I77" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0252102154806206</v>
+        <v>0.02361385827369711</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7563064644186179</v>
+        <v>0.7084157482109134</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>87.24895664584963</v>
+        <v>85.26617543902816</v>
       </c>
       <c r="D78" t="n">
-        <v>14.82700956436264</v>
+        <v>16.69490697691029</v>
       </c>
       <c r="E78" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F78" t="n">
-        <v>74.69653390481575</v>
+        <v>74.4304941166956</v>
       </c>
       <c r="G78" t="n">
-        <v>9.070216032130523</v>
+        <v>9.345250888825685</v>
       </c>
       <c r="H78" t="n">
         <v>14</v>
       </c>
       <c r="I78" t="n">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="J78" t="n">
-        <v>0.004069261242278246</v>
+        <v>0.01704675424721766</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1220778372683474</v>
+        <v>0.5114026274165299</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3568,31 +3580,31 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>98.72662531390932</v>
+        <v>98.57470310980909</v>
       </c>
       <c r="D79" t="n">
-        <v>13.04012057798121</v>
+        <v>13.11755668639216</v>
       </c>
       <c r="E79" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F79" t="n">
-        <v>68.22057539120938</v>
+        <v>68.05698030811529</v>
       </c>
       <c r="G79" t="n">
-        <v>5.415665065981627</v>
+        <v>5.755583790702577</v>
       </c>
       <c r="H79" t="n">
         <v>14</v>
       </c>
       <c r="I79" t="n">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="J79" t="n">
-        <v>7.58448007594608e-08</v>
+        <v>8.466361340134886e-08</v>
       </c>
       <c r="K79" t="n">
-        <v>2.275344022783824e-06</v>
+        <v>2.539908402040466e-06</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>96.06939891960877</v>
+        <v>97.05536802077283</v>
       </c>
       <c r="D80" t="n">
-        <v>12.19621398867989</v>
+        <v>11.96321433766867</v>
       </c>
       <c r="E80" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F80" t="n">
-        <v>106.0326019974928</v>
+        <v>105.8041191217498</v>
       </c>
       <c r="G80" t="n">
-        <v>10.08347083655077</v>
+        <v>10.39351530904916</v>
       </c>
       <c r="H80" t="n">
         <v>14</v>
       </c>
       <c r="I80" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="J80" t="n">
-        <v>0.008054347652564636</v>
+        <v>0.02056989017408441</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2416304295769391</v>
+        <v>0.6170967052225323</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>86.73997506790066</v>
+        <v>84.43090328455907</v>
       </c>
       <c r="D81" t="n">
-        <v>20.09475027897387</v>
+        <v>20.34352216675695</v>
       </c>
       <c r="E81" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F81" t="n">
-        <v>63.9753572439448</v>
+        <v>63.81310460555574</v>
       </c>
       <c r="G81" t="n">
-        <v>8.474078769377305</v>
+        <v>8.760122780009779</v>
       </c>
       <c r="H81" t="n">
         <v>14</v>
       </c>
       <c r="I81" t="n">
-        <v>551</v>
+        <v>516</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0001453515098236909</v>
+        <v>0.0007198026495289682</v>
       </c>
       <c r="K81" t="n">
-        <v>0.004360545294710726</v>
+        <v>0.02159407948586905</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,31 +3700,31 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>91.13040632094935</v>
+        <v>90.6819493225363</v>
       </c>
       <c r="D82" t="n">
-        <v>20.85803685078786</v>
+        <v>20.63673338532793</v>
       </c>
       <c r="E82" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n">
-        <v>71.22833528769551</v>
+        <v>72.9707088269782</v>
       </c>
       <c r="G82" t="n">
-        <v>14.6506746533748</v>
+        <v>14.99197014143008</v>
       </c>
       <c r="H82" t="n">
         <v>14</v>
       </c>
       <c r="I82" t="n">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="J82" t="n">
-        <v>0.001963481019681228</v>
+        <v>0.005308638546158322</v>
       </c>
       <c r="K82" t="n">
-        <v>0.05890443059043685</v>
+        <v>0.1592591563847497</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3728,31 +3740,31 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>93.77137469813471</v>
+        <v>92.34476624127772</v>
       </c>
       <c r="D83" t="n">
-        <v>14.57798915472792</v>
+        <v>15.86557175075252</v>
       </c>
       <c r="E83" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>73.97825724798831</v>
+        <v>75.413950911811</v>
       </c>
       <c r="G83" t="n">
-        <v>11.37934915745297</v>
+        <v>14.61545146788614</v>
       </c>
       <c r="H83" t="n">
         <v>14</v>
       </c>
       <c r="I83" t="n">
-        <v>555</v>
+        <v>504</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0001099646350540217</v>
+        <v>0.00151293191022734</v>
       </c>
       <c r="K83" t="n">
-        <v>0.003298939051620652</v>
+        <v>0.04538795730682019</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -3768,28 +3780,28 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>77.79641796797358</v>
+        <v>77.06385114264258</v>
       </c>
       <c r="D84" t="n">
-        <v>17.71946765434195</v>
+        <v>17.6251146270642</v>
       </c>
       <c r="E84" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F84" t="n">
-        <v>61.8763636731227</v>
+        <v>61.84415753507732</v>
       </c>
       <c r="G84" t="n">
-        <v>38.17631421516946</v>
+        <v>38.17551730895948</v>
       </c>
       <c r="H84" t="n">
         <v>14</v>
       </c>
       <c r="I84" t="n">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="J84" t="n">
-        <v>0.2612800453756595</v>
+        <v>0.2903303595006221</v>
       </c>
       <c r="K84" t="n">
         <v>1</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>84.89566663254041</v>
+        <v>85.94473362950544</v>
       </c>
       <c r="D85" t="n">
-        <v>23.22759592248585</v>
+        <v>23.30251578692695</v>
       </c>
       <c r="E85" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F85" t="n">
-        <v>66.02776070518777</v>
+        <v>66.43940156079408</v>
       </c>
       <c r="G85" t="n">
-        <v>13.03873392430578</v>
+        <v>14.01034637954016</v>
       </c>
       <c r="H85" t="n">
         <v>14</v>
       </c>
       <c r="I85" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J85" t="n">
-        <v>0.008472600895518588</v>
+        <v>0.005910094312329881</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2541780268655576</v>
+        <v>0.1773028293698964</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>62.83377335878728</v>
+        <v>64.57488770474643</v>
       </c>
       <c r="D86" t="n">
-        <v>18.95486741832631</v>
+        <v>20.74122269359543</v>
       </c>
       <c r="E86" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F86" t="n">
-        <v>71.39383486312705</v>
+        <v>71.16291577372509</v>
       </c>
       <c r="G86" t="n">
-        <v>42.47309036995517</v>
+        <v>42.36054467347275</v>
       </c>
       <c r="H86" t="n">
         <v>14</v>
       </c>
       <c r="I86" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J86" t="n">
-        <v>0.7251462648018774</v>
+        <v>0.8407041634748884</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>104.9015885480963</v>
+        <v>105.5337263564648</v>
       </c>
       <c r="D87" t="n">
-        <v>14.1302351999723</v>
+        <v>13.74522471368201</v>
       </c>
       <c r="E87" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F87" t="n">
-        <v>83.25435364522257</v>
+        <v>82.94365533136546</v>
       </c>
       <c r="G87" t="n">
-        <v>5.204726547182312</v>
+        <v>5.69113353783486</v>
       </c>
       <c r="H87" t="n">
         <v>14</v>
       </c>
       <c r="I87" t="n">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J87" t="n">
-        <v>9.273454421359449e-06</v>
+        <v>4.117569746122576e-06</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0002782036326407835</v>
+        <v>0.0001235270923836773</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,31 +3940,31 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>78.47505236343035</v>
+        <v>75.58159957666214</v>
       </c>
       <c r="D88" t="n">
-        <v>22.60403859715451</v>
+        <v>21.32257595713245</v>
       </c>
       <c r="E88" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F88" t="n">
-        <v>114.3411103473369</v>
+        <v>114.3291104282071</v>
       </c>
       <c r="G88" t="n">
-        <v>8.652674676442821</v>
+        <v>8.650593497135302</v>
       </c>
       <c r="H88" t="n">
         <v>14</v>
       </c>
       <c r="I88" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>1.064231198282463e-06</v>
+        <v>2.408990124585967e-07</v>
       </c>
       <c r="K88" t="n">
-        <v>3.192693594847388e-05</v>
+        <v>7.2269703737579e-06</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>95.05027515642767</v>
+        <v>92.73819392313452</v>
       </c>
       <c r="D89" t="n">
-        <v>21.53984326691825</v>
+        <v>21.23929659520199</v>
       </c>
       <c r="E89" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F89" t="n">
-        <v>20.00330556791067</v>
+        <v>22.66192996643883</v>
       </c>
       <c r="G89" t="n">
-        <v>5.395809626314221</v>
+        <v>8.649129104483155</v>
       </c>
       <c r="H89" t="n">
         <v>14</v>
       </c>
       <c r="I89" t="n">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="J89" t="n">
-        <v>1.760722132370437e-08</v>
+        <v>1.919980325303849e-08</v>
       </c>
       <c r="K89" t="n">
-        <v>5.28216639711131e-07</v>
+        <v>5.759940975911548e-07</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,31 +4020,31 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>78.78258462761428</v>
+        <v>79.17919996554215</v>
       </c>
       <c r="D90" t="n">
-        <v>17.6882776011221</v>
+        <v>18.11614220103742</v>
       </c>
       <c r="E90" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F90" t="n">
-        <v>104.5286235898261</v>
+        <v>104.5412939226069</v>
       </c>
       <c r="G90" t="n">
-        <v>11.25731150966967</v>
+        <v>11.2768693862664</v>
       </c>
       <c r="H90" t="n">
         <v>14</v>
       </c>
       <c r="I90" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J90" t="n">
-        <v>2.548098829299995e-05</v>
+        <v>3.855309649366076e-05</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0007644296487899986</v>
+        <v>0.001156592894809823</v>
       </c>
       <c r="L90" t="b">
         <v>1</v>
@@ -4048,28 +4060,28 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>79.65836134681503</v>
+        <v>79.49729285371455</v>
       </c>
       <c r="D91" t="n">
-        <v>17.50423394598493</v>
+        <v>17.23428932973591</v>
       </c>
       <c r="E91" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F91" t="n">
-        <v>91.21867736848461</v>
+        <v>90.97437831062201</v>
       </c>
       <c r="G91" t="n">
-        <v>24.88550168668699</v>
+        <v>24.9370624828913</v>
       </c>
       <c r="H91" t="n">
         <v>14</v>
       </c>
       <c r="I91" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J91" t="n">
-        <v>0.05158218484155815</v>
+        <v>0.04728794848895175</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>11.24291691765153</v>
+        <v>11.68147646401331</v>
       </c>
       <c r="D92" t="n">
-        <v>4.256650920899587</v>
+        <v>4.091228866506352</v>
       </c>
       <c r="E92" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F92" t="n">
-        <v>10.71736553391284</v>
+        <v>10.6277567291153</v>
       </c>
       <c r="G92" t="n">
-        <v>1.400976433271519</v>
+        <v>1.412123583360496</v>
       </c>
       <c r="H92" t="n">
         <v>14</v>
       </c>
       <c r="I92" t="n">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="J92" t="n">
-        <v>0.2761232815108396</v>
+        <v>0.07321982439601583</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,28 +4140,28 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>11.72905805078778</v>
+        <v>12.07407186009986</v>
       </c>
       <c r="D93" t="n">
-        <v>5.505105355568211</v>
+        <v>5.479858429096976</v>
       </c>
       <c r="E93" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F93" t="n">
-        <v>13.8098221065191</v>
+        <v>13.65352532812665</v>
       </c>
       <c r="G93" t="n">
-        <v>0.7304003294311174</v>
+        <v>1.203009414520133</v>
       </c>
       <c r="H93" t="n">
         <v>14</v>
       </c>
       <c r="I93" t="n">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="J93" t="n">
-        <v>0.06776753662940209</v>
+        <v>0.1869813752896539</v>
       </c>
       <c r="K93" t="n">
         <v>1</v>
@@ -4168,28 +4180,28 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>13.57019303335153</v>
+        <v>13.77168689898457</v>
       </c>
       <c r="D94" t="n">
-        <v>4.261528603076477</v>
+        <v>4.195654367192767</v>
       </c>
       <c r="E94" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F94" t="n">
-        <v>13.31255520431402</v>
+        <v>13.24783521609094</v>
       </c>
       <c r="G94" t="n">
-        <v>1.953184905537941</v>
+        <v>2.150184716049238</v>
       </c>
       <c r="H94" t="n">
         <v>14</v>
       </c>
       <c r="I94" t="n">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7640724767611864</v>
+        <v>0.5465229553287476</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>12.34000560821426</v>
+        <v>12.68263215853832</v>
       </c>
       <c r="D95" t="n">
-        <v>3.366235930804471</v>
+        <v>3.489625575560392</v>
       </c>
       <c r="E95" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F95" t="n">
-        <v>16.22353640772933</v>
+        <v>16.17309554801415</v>
       </c>
       <c r="G95" t="n">
-        <v>1.938343710969871</v>
+        <v>2.025577935071638</v>
       </c>
       <c r="H95" t="n">
         <v>14</v>
       </c>
       <c r="I95" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0001024844180086673</v>
+        <v>0.0005567906609930178</v>
       </c>
       <c r="K95" t="n">
-        <v>0.003074532540260019</v>
+        <v>0.01670371982979053</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,31 +4260,31 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>15.71662385498953</v>
+        <v>16.30203183878281</v>
       </c>
       <c r="D96" t="n">
-        <v>4.860405351567212</v>
+        <v>4.427561292253697</v>
       </c>
       <c r="E96" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F96" t="n">
-        <v>13.97004129670087</v>
+        <v>13.88220329133927</v>
       </c>
       <c r="G96" t="n">
-        <v>1.953421697920657</v>
+        <v>1.921202713728134</v>
       </c>
       <c r="H96" t="n">
         <v>14</v>
       </c>
       <c r="I96" t="n">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="J96" t="n">
-        <v>0.05367456685503969</v>
+        <v>0.009447280011616745</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0.2834184003485024</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4288,28 +4300,28 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>11.82636737727124</v>
+        <v>12.29897046270223</v>
       </c>
       <c r="D97" t="n">
-        <v>5.052457014993851</v>
+        <v>5.272398891212139</v>
       </c>
       <c r="E97" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F97" t="n">
-        <v>12.64358390280938</v>
+        <v>12.65714014535195</v>
       </c>
       <c r="G97" t="n">
-        <v>1.354149851994696</v>
+        <v>1.390403703344847</v>
       </c>
       <c r="H97" t="n">
         <v>14</v>
       </c>
       <c r="I97" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6009072212136328</v>
+        <v>0.951222437778796</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
@@ -4328,28 +4340,28 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>13.21823973616002</v>
+        <v>13.78049951187761</v>
       </c>
       <c r="D98" t="n">
-        <v>4.212844533232752</v>
+        <v>4.2847150300273</v>
       </c>
       <c r="E98" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F98" t="n">
-        <v>11.48255504935456</v>
+        <v>11.51604605395685</v>
       </c>
       <c r="G98" t="n">
-        <v>1.981302702934643</v>
+        <v>2.008910097989291</v>
       </c>
       <c r="H98" t="n">
         <v>14</v>
       </c>
       <c r="I98" t="n">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="J98" t="n">
-        <v>0.2332715977139465</v>
+        <v>0.08836804219518533</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -4368,28 +4380,28 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>13.06641810506974</v>
+        <v>13.8203607153468</v>
       </c>
       <c r="D99" t="n">
-        <v>4.415434780326399</v>
+        <v>4.062198526293208</v>
       </c>
       <c r="E99" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F99" t="n">
-        <v>15.03277392961735</v>
+        <v>14.97882285032459</v>
       </c>
       <c r="G99" t="n">
-        <v>2.528260928528771</v>
+        <v>2.576289522851549</v>
       </c>
       <c r="H99" t="n">
         <v>14</v>
       </c>
       <c r="I99" t="n">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3588480050183636</v>
+        <v>0.7464405454688596</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -4408,28 +4420,28 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>12.79249607078809</v>
+        <v>12.98511026377467</v>
       </c>
       <c r="D100" t="n">
-        <v>2.863438419188689</v>
+        <v>2.716790140136358</v>
       </c>
       <c r="E100" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F100" t="n">
-        <v>12.24222180899691</v>
+        <v>12.31582446190317</v>
       </c>
       <c r="G100" t="n">
-        <v>1.74601243359789</v>
+        <v>1.749330744862489</v>
       </c>
       <c r="H100" t="n">
         <v>14</v>
       </c>
       <c r="I100" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J100" t="n">
-        <v>0.2332715977139465</v>
+        <v>0.1543227288855238</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4448,28 +4460,28 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>12.52287655235598</v>
+        <v>13.08034152058363</v>
       </c>
       <c r="D101" t="n">
-        <v>3.117726536706384</v>
+        <v>3.068377208413495</v>
       </c>
       <c r="E101" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F101" t="n">
-        <v>13.63052314319802</v>
+        <v>13.65604109525355</v>
       </c>
       <c r="G101" t="n">
-        <v>1.973877977403848</v>
+        <v>1.945593423210618</v>
       </c>
       <c r="H101" t="n">
         <v>14</v>
       </c>
       <c r="I101" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1088043725300085</v>
+        <v>0.2824307785502602</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>13.08389577029858</v>
+        <v>13.5121527139131</v>
       </c>
       <c r="D102" t="n">
-        <v>3.920080181255539</v>
+        <v>3.642090753000668</v>
       </c>
       <c r="E102" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F102" t="n">
-        <v>17.23197395131168</v>
+        <v>17.15160964157868</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7037213096771961</v>
+        <v>0.9624864362087188</v>
       </c>
       <c r="H102" t="n">
         <v>14</v>
       </c>
       <c r="I102" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J102" t="n">
-        <v>7.294545087771673e-06</v>
+        <v>1.404264328299813e-05</v>
       </c>
       <c r="K102" t="n">
-        <v>0.0002188363526331502</v>
+        <v>0.000421279298489944</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,31 +4540,31 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>14.92104372791617</v>
+        <v>15.53698257851219</v>
       </c>
       <c r="D103" t="n">
-        <v>3.078407351016157</v>
+        <v>3.281972740240438</v>
       </c>
       <c r="E103" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F103" t="n">
-        <v>13.06203996404935</v>
+        <v>13.07321447941358</v>
       </c>
       <c r="G103" t="n">
-        <v>1.653515794562215</v>
+        <v>1.658005795442379</v>
       </c>
       <c r="H103" t="n">
         <v>14</v>
       </c>
       <c r="I103" t="n">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="J103" t="n">
-        <v>0.03416563784278469</v>
+        <v>0.006927796090833134</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0.207833882724994</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4568,28 +4580,28 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>12.94046407396377</v>
+        <v>13.40562779137599</v>
       </c>
       <c r="D104" t="n">
-        <v>4.235990894534898</v>
+        <v>4.108342165119254</v>
       </c>
       <c r="E104" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F104" t="n">
-        <v>11.07784234422694</v>
+        <v>10.97266204887418</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5314784161287517</v>
+        <v>0.8373009991865922</v>
       </c>
       <c r="H104" t="n">
         <v>14</v>
       </c>
       <c r="I104" t="n">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="J104" t="n">
-        <v>0.1334367479717718</v>
+        <v>0.03519952873291349</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -4608,28 +4620,28 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>15.03884784660721</v>
+        <v>15.35854060847866</v>
       </c>
       <c r="D105" t="n">
-        <v>2.46691802589258</v>
+        <v>2.560685168932675</v>
       </c>
       <c r="E105" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F105" t="n">
-        <v>15.50580207025859</v>
+        <v>15.55844800334708</v>
       </c>
       <c r="G105" t="n">
-        <v>2.290332939425797</v>
+        <v>2.166613673107863</v>
       </c>
       <c r="H105" t="n">
         <v>14</v>
       </c>
       <c r="I105" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="J105" t="n">
-        <v>0.3864296705094658</v>
+        <v>0.5819451837145403</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -4648,28 +4660,28 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.27224499357245</v>
+        <v>11.75035324023634</v>
       </c>
       <c r="D106" t="n">
-        <v>2.764716393788381</v>
+        <v>2.809106695039655</v>
       </c>
       <c r="E106" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F106" t="n">
-        <v>12.27576162583481</v>
+        <v>12.40416453597381</v>
       </c>
       <c r="G106" t="n">
-        <v>2.656466757424269</v>
+        <v>2.589996504080356</v>
       </c>
       <c r="H106" t="n">
         <v>14</v>
       </c>
       <c r="I106" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="J106" t="n">
-        <v>0.2612800453756595</v>
+        <v>0.4682544935914651</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -4688,28 +4700,28 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>14.38726554548535</v>
+        <v>14.73472943401383</v>
       </c>
       <c r="D107" t="n">
-        <v>3.578244954561633</v>
+        <v>3.750789104278653</v>
       </c>
       <c r="E107" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F107" t="n">
-        <v>16.01317426742902</v>
+        <v>15.99818736150491</v>
       </c>
       <c r="G107" t="n">
-        <v>1.402391025875684</v>
+        <v>1.385468174066711</v>
       </c>
       <c r="H107" t="n">
         <v>14</v>
       </c>
       <c r="I107" t="n">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="J107" t="n">
-        <v>0.06276523953911908</v>
+        <v>0.1928876287572029</v>
       </c>
       <c r="K107" t="n">
         <v>1</v>
@@ -4728,28 +4740,28 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>13.35239053019547</v>
+        <v>14.05612239844928</v>
       </c>
       <c r="D108" t="n">
-        <v>4.820278531603886</v>
+        <v>4.888735521612256</v>
       </c>
       <c r="E108" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F108" t="n">
-        <v>13.42413106472651</v>
+        <v>13.40254482202898</v>
       </c>
       <c r="G108" t="n">
-        <v>1.251961884491311</v>
+        <v>1.249871315067786</v>
       </c>
       <c r="H108" t="n">
         <v>14</v>
       </c>
       <c r="I108" t="n">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5313145984023002</v>
+        <v>0.979084688069229</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -4768,31 +4780,31 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>12.95685633047379</v>
+        <v>13.41516374500672</v>
       </c>
       <c r="D109" t="n">
-        <v>4.617450632870447</v>
+        <v>4.179373879098779</v>
       </c>
       <c r="E109" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F109" t="n">
-        <v>11.67521113228887</v>
+        <v>11.63281809306863</v>
       </c>
       <c r="G109" t="n">
-        <v>1.593816300736286</v>
+        <v>1.678238494339985</v>
       </c>
       <c r="H109" t="n">
         <v>14</v>
       </c>
       <c r="I109" t="n">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="J109" t="n">
-        <v>0.06522684825505155</v>
+        <v>0.02585391914073909</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>0.7756175742221727</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4808,28 +4820,28 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>13.31623116459298</v>
+        <v>13.82883659455657</v>
       </c>
       <c r="D110" t="n">
-        <v>3.414031124184146</v>
+        <v>3.684323792189648</v>
       </c>
       <c r="E110" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F110" t="n">
-        <v>14.98162451768857</v>
+        <v>14.90170726604988</v>
       </c>
       <c r="G110" t="n">
-        <v>2.304136364528852</v>
+        <v>2.288392334806722</v>
       </c>
       <c r="H110" t="n">
         <v>14</v>
       </c>
       <c r="I110" t="n">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="J110" t="n">
-        <v>0.04211744071317501</v>
+        <v>0.1493291075014022</v>
       </c>
       <c r="K110" t="n">
         <v>1</v>
@@ -4848,28 +4860,28 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>13.37240146967521</v>
+        <v>13.72814084334333</v>
       </c>
       <c r="D111" t="n">
-        <v>3.28862842985256</v>
+        <v>3.182523646429862</v>
       </c>
       <c r="E111" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F111" t="n">
-        <v>13.04058388731343</v>
+        <v>13.13595950908834</v>
       </c>
       <c r="G111" t="n">
-        <v>1.405011219672596</v>
+        <v>1.356972285002581</v>
       </c>
       <c r="H111" t="n">
         <v>14</v>
       </c>
       <c r="I111" t="n">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="J111" t="n">
-        <v>0.3325379506593946</v>
+        <v>0.1989298305258246</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>12.41426413535411</v>
+        <v>12.92593898706354</v>
       </c>
       <c r="D112" t="n">
-        <v>3.79329730052576</v>
+        <v>3.861142548814696</v>
       </c>
       <c r="E112" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F112" t="n">
-        <v>15.99308338369512</v>
+        <v>15.82923310554285</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8808412847739319</v>
+        <v>1.200734000732093</v>
       </c>
       <c r="H112" t="n">
         <v>14</v>
       </c>
       <c r="I112" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="J112" t="n">
-        <v>0.002203047020035315</v>
+        <v>0.01155275748398303</v>
       </c>
       <c r="K112" t="n">
-        <v>0.06609141060105944</v>
+        <v>0.346582724519491</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>12.03829752615433</v>
+        <v>12.29021715549642</v>
       </c>
       <c r="D113" t="n">
-        <v>4.559304518261612</v>
+        <v>4.781762667133235</v>
       </c>
       <c r="E113" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F113" t="n">
-        <v>14.02642795159061</v>
+        <v>14.01047332372579</v>
       </c>
       <c r="G113" t="n">
-        <v>1.070907809648847</v>
+        <v>1.089834492595632</v>
       </c>
       <c r="H113" t="n">
         <v>14</v>
       </c>
       <c r="I113" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J113" t="n">
-        <v>0.02876339761688703</v>
+        <v>0.05564552356859782</v>
       </c>
       <c r="K113" t="n">
-        <v>0.862901928506611</v>
+        <v>1</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4968,31 +4980,31 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>16.55780338016072</v>
+        <v>17.07770129741503</v>
       </c>
       <c r="D114" t="n">
-        <v>3.154424203790902</v>
+        <v>2.683203168540368</v>
       </c>
       <c r="E114" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F114" t="n">
-        <v>13.63878015898838</v>
+        <v>13.71202369330415</v>
       </c>
       <c r="G114" t="n">
-        <v>3.990817671663685</v>
+        <v>3.916505694623888</v>
       </c>
       <c r="H114" t="n">
         <v>14</v>
       </c>
       <c r="I114" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J114" t="n">
-        <v>0.008910171236468527</v>
+        <v>0.005029143592893</v>
       </c>
       <c r="K114" t="n">
-        <v>0.2673051370940558</v>
+        <v>0.15087430778679</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.26820200187859</v>
+        <v>12.72620686483958</v>
       </c>
       <c r="D115" t="n">
-        <v>3.186121432813787</v>
+        <v>3.262944653775512</v>
       </c>
       <c r="E115" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F115" t="n">
-        <v>14.48476205972133</v>
+        <v>14.30687400244831</v>
       </c>
       <c r="G115" t="n">
-        <v>1.343946222282769</v>
+        <v>1.772475569315292</v>
       </c>
       <c r="H115" t="n">
         <v>14</v>
       </c>
       <c r="I115" t="n">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="J115" t="n">
-        <v>0.005608419185777522</v>
+        <v>0.04173579952502548</v>
       </c>
       <c r="K115" t="n">
-        <v>0.1682525755733257</v>
+        <v>1</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -5048,28 +5060,28 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>13.61444149801631</v>
+        <v>13.81084739927461</v>
       </c>
       <c r="D116" t="n">
-        <v>2.959982447318706</v>
+        <v>2.729032270923568</v>
       </c>
       <c r="E116" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F116" t="n">
-        <v>14.8872243658283</v>
+        <v>14.96551338075089</v>
       </c>
       <c r="G116" t="n">
-        <v>2.795246671272675</v>
+        <v>2.80832828385417</v>
       </c>
       <c r="H116" t="n">
         <v>14</v>
       </c>
       <c r="I116" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J116" t="n">
-        <v>0.1837888581953325</v>
+        <v>0.1928876287572029</v>
       </c>
       <c r="K116" t="n">
         <v>1</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>10.72148915399045</v>
+        <v>10.88222715846759</v>
       </c>
       <c r="D117" t="n">
-        <v>3.735417412742938</v>
+        <v>3.784976335393824</v>
       </c>
       <c r="E117" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F117" t="n">
-        <v>14.89470968341775</v>
+        <v>14.97363054561228</v>
       </c>
       <c r="G117" t="n">
-        <v>1.826024422209964</v>
+        <v>1.863244450938892</v>
       </c>
       <c r="H117" t="n">
         <v>14</v>
       </c>
       <c r="I117" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J117" t="n">
-        <v>9.548631395808657e-05</v>
+        <v>0.0002506788194625127</v>
       </c>
       <c r="K117" t="n">
-        <v>0.002864589418742597</v>
+        <v>0.00752036458387538</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,31 +5140,31 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>14.23296767660491</v>
+        <v>15.00406165494858</v>
       </c>
       <c r="D118" t="n">
-        <v>5.023256675077371</v>
+        <v>4.608276740480807</v>
       </c>
       <c r="E118" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F118" t="n">
-        <v>11.87241868191295</v>
+        <v>11.85989144711422</v>
       </c>
       <c r="G118" t="n">
-        <v>1.449844974093044</v>
+        <v>1.454474613884069</v>
       </c>
       <c r="H118" t="n">
         <v>14</v>
       </c>
       <c r="I118" t="n">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="J118" t="n">
-        <v>0.1247868780433192</v>
+        <v>0.02955779618301077</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0.8867338854903231</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>12.64050251429752</v>
+        <v>13.09362299245182</v>
       </c>
       <c r="D119" t="n">
-        <v>3.79502550927653</v>
+        <v>3.881119092503527</v>
       </c>
       <c r="E119" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F119" t="n">
-        <v>17.99446650699216</v>
+        <v>17.97388704318933</v>
       </c>
       <c r="G119" t="n">
-        <v>1.563071154510895</v>
+        <v>1.558247123286767</v>
       </c>
       <c r="H119" t="n">
         <v>14</v>
       </c>
       <c r="I119" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J119" t="n">
-        <v>4.479156100899939e-06</v>
+        <v>1.520373944555459e-05</v>
       </c>
       <c r="K119" t="n">
-        <v>0.0001343746830269982</v>
+        <v>0.0004561121833666376</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,28 +5220,28 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>15.03415992543407</v>
+        <v>15.36937580830998</v>
       </c>
       <c r="D120" t="n">
-        <v>4.490452585254572</v>
+        <v>4.598016269670079</v>
       </c>
       <c r="E120" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F120" t="n">
-        <v>14.85636444410102</v>
+        <v>14.83645290890825</v>
       </c>
       <c r="G120" t="n">
-        <v>2.577044113514175</v>
+        <v>2.606779738644024</v>
       </c>
       <c r="H120" t="n">
         <v>14</v>
       </c>
       <c r="I120" t="n">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="J120" t="n">
-        <v>0.3325379506593946</v>
+        <v>0.1812097745772908</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -5248,28 +5260,28 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.88389733380891</v>
+        <v>15.16445622780817</v>
       </c>
       <c r="D121" t="n">
-        <v>2.976644861987177</v>
+        <v>2.702642423610264</v>
       </c>
       <c r="E121" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F121" t="n">
-        <v>13.82893069612913</v>
+        <v>13.82268909835428</v>
       </c>
       <c r="G121" t="n">
-        <v>3.488885096953358</v>
+        <v>3.495173458039292</v>
       </c>
       <c r="H121" t="n">
         <v>14</v>
       </c>
       <c r="I121" t="n">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="J121" t="n">
-        <v>0.09448623541275779</v>
+        <v>0.04001223149349032</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
